--- a/DataTables/DetailText/剧情/027_上元灯节.xlsx
+++ b/DataTables/DetailText/剧情/027_上元灯节.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526E89B7-D6DF-4DF3-9513-E2226FE48F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9A8042-025F-42B1-B578-6AB3B5B8A9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="79">
   <si>
     <t>LineIndex</t>
   </si>
@@ -1491,7 +1491,9 @@
       <c r="B2" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="D2" s="23">
         <v>26</v>
       </c>

--- a/DataTables/DetailText/剧情/027_上元灯节.xlsx
+++ b/DataTables/DetailText/剧情/027_上元灯节.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9A8042-025F-42B1-B578-6AB3B5B8A9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87816FD2-9C05-406E-B5FE-CE2A63B5C94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="82">
   <si>
     <t>LineIndex</t>
   </si>
@@ -738,6 +738,157 @@
   </si>
   <si>
     <r>
+      <t>干了一年坐堂医，感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>觉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>怎么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，和你之前想的一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样吗？</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>我倒是挺喜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欢这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一行，只是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赚不到什么钱，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>苦了您和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芷兰了…</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>是啊，一家人平平安安就好啊。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>好了，不早了，咱们该回家了。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个我会，是"忍冬"。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
       <t>res://Assets/Background/0</t>
     </r>
     <r>
@@ -778,179 +929,62 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>干了一年坐堂医，感</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>觉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>怎么</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>样</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，和你之前想的一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>样吗？</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>我倒是挺喜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>欢这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一行，只是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赚不到什么钱，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>苦了您和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>芷兰了…</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>是啊，一家人平平安安就好啊。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>好了，不早了，咱们该回家了。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>个我会，是"忍冬"。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+      <t>06.png</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>哇，放烟花啦！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>真漂亮啊。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>027_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>05.png</t>
+    </r>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1098,7 +1132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1189,6 +1223,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1755,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1820,7 +1860,7 @@
         <v>38</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2272,7 +2312,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I23" s="3"/>
     </row>
@@ -2284,18 +2324,20 @@
         <v>9</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1">
@@ -2305,20 +2347,18 @@
         <v>9</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I25" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1">
@@ -2328,16 +2368,16 @@
         <v>9</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>35</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>73</v>
+      <c r="H26" s="31" t="s">
+        <v>70</v>
       </c>
       <c r="I26" s="3"/>
     </row>
@@ -2349,16 +2389,18 @@
         <v>9</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="H27" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I27" s="3"/>
     </row>
@@ -2370,16 +2412,16 @@
         <v>9</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I28" s="3"/>
     </row>
@@ -2391,16 +2433,16 @@
         <v>9</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I29" s="3"/>
     </row>
@@ -2408,26 +2450,42 @@
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="H30" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="2"/>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9">
@@ -2444,7 +2502,9 @@
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="3"/>
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="2"/>
@@ -2455,7 +2515,9 @@
       <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="3"/>
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="2"/>
@@ -2476,6 +2538,28 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
